--- a/tools/importer/reports/import-adventures-page.report.xlsx
+++ b/tools/importer/reports/import-adventures-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,10 +61,31 @@
     <t>https://wknd.site/us/en.html</t>
   </si>
   <si>
+    <t>us/en/about-us.report.json</t>
+  </si>
+  <si>
+    <t>["cards-profile","cards-profile","cards-profile","cards-profile","cards-profile","cards-profile","cards-profile"]</t>
+  </si>
+  <si>
+    <t>us/en/about-us</t>
+  </si>
+  <si>
+    <t>about-us-page</t>
+  </si>
+  <si>
+    <t>2026-08-09T10:32:19.774Z</t>
+  </si>
+  <si>
+    <t>About Us</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/about-us.html</t>
+  </si>
+  <si>
     <t>us/en/adventures.report.json</t>
   </si>
   <si>
-    <t>["hero-intro","tabs-adventures"]</t>
+    <t>["hero-intro","cards-article"]</t>
   </si>
   <si>
     <t>us/en/adventures</t>
@@ -73,7 +94,7 @@
     <t>adventures-page</t>
   </si>
   <si>
-    <t>2026-08-08T18:23:27.011Z</t>
+    <t>2026-08-10T13:14:17.969Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -82,6 +103,27 @@
     <t>https://wknd.site/us/en/adventures.html</t>
   </si>
   <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>faqs-page</t>
+  </si>
+  <si>
+    <t>2026-08-08T19:06:59.193Z</t>
+  </si>
+  <si>
+    <t>FAQs</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/faqs.html</t>
+  </si>
+  <si>
     <t>us/en/magazine.report.json</t>
   </si>
   <si>
@@ -101,6 +143,90 @@
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing.report.json</t>
+  </si>
+  <si>
+    <t>["quote-pull","cards-profile"]</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing</t>
+  </si>
+  <si>
+    <t>article-page</t>
+  </si>
+  <si>
+    <t>2026-08-10T09:46:45.013Z</t>
+  </si>
+  <si>
+    <t>Arctic Surfing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/arctic-surfing.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/guide-la-skateparks.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/guide-la-skateparks</t>
+  </si>
+  <si>
+    <t>2026-08-10T11:33:22.273Z</t>
+  </si>
+  <si>
+    <t>Ultimate Guide to LA Skateparks</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/guide-la-skateparks.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/san-diego-surf.report.json</t>
+  </si>
+  <si>
+    <t>["cards-profile"]</t>
+  </si>
+  <si>
+    <t>us/en/magazine/san-diego-surf</t>
+  </si>
+  <si>
+    <t>2026-08-10T10:47:30.305Z</t>
+  </si>
+  <si>
+    <t>San Diego Surf Spots</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/san-diego-surf.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/ski-touring.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/ski-touring</t>
+  </si>
+  <si>
+    <t>2026-08-10T11:10:18.530Z</t>
+  </si>
+  <si>
+    <t>Ski Touring</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/ski-touring.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/western-australia.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/western-australia</t>
+  </si>
+  <si>
+    <t>2026-08-10T09:12:53.491Z</t>
+  </si>
+  <si>
+    <t>Western Australia</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/western-australia.html</t>
   </si>
 </sst>
 </file>
@@ -489,16 +615,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="41" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -603,6 +729,188 @@
       </c>
       <c r="H4" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
